--- a/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="110">
   <si>
     <t>TC ID</t>
   </si>
@@ -191,7 +191,7 @@
     <t>0400123146</t>
   </si>
   <si>
-    <t>1 Sydney St, Mogo NSW 2536</t>
+    <t>neil.jones@exxonmobil.com.test</t>
   </si>
   <si>
     <t>Guild Insurance Ltd</t>
@@ -278,10 +278,85 @@
     <t>${TC001.Vehicle name}</t>
   </si>
   <si>
-    <t>neil.jones@exxonmobil.com.test</t>
-  </si>
-  <si>
     <t>Your Residential Address *</t>
+  </si>
+  <si>
+    <t>06 Jan 2027</t>
+  </si>
+  <si>
+    <t>01 Jun 2000</t>
+  </si>
+  <si>
+    <t>REQ-925</t>
+  </si>
+  <si>
+    <t>CYP806</t>
+  </si>
+  <si>
+    <t>TESLA MODEL Y</t>
+  </si>
+  <si>
+    <t>11 Jun 2027</t>
+  </si>
+  <si>
+    <t>8066</t>
+  </si>
+  <si>
+    <t>Neeti</t>
+  </si>
+  <si>
+    <t>Tripathi</t>
+  </si>
+  <si>
+    <t>03 Jul 1993</t>
+  </si>
+  <si>
+    <t>0499656877</t>
+  </si>
+  <si>
+    <t>neeti.tripathi@kmart.com.au.test</t>
+  </si>
+  <si>
+    <t>Kmart Australia Limited</t>
+  </si>
+  <si>
+    <t>FPJ50N</t>
+  </si>
+  <si>
+    <t>BYD DOLPHIN</t>
+  </si>
+  <si>
+    <t>8956</t>
+  </si>
+  <si>
+    <t>Sudeep</t>
+  </si>
+  <si>
+    <t>Shakya</t>
+  </si>
+  <si>
+    <t>27 Jun 1986</t>
+  </si>
+  <si>
+    <t>333665987</t>
+  </si>
+  <si>
+    <t>sudeep.shakya@outlook.com.test</t>
+  </si>
+  <si>
+    <t>QBE Management Services Pty Ltd</t>
+  </si>
+  <si>
+    <t>REQ-163</t>
+  </si>
+  <si>
+    <t>29 Jul 2026 07:17 PM</t>
+  </si>
+  <si>
+    <t>REQ-164</t>
+  </si>
+  <si>
+    <t>29 Jul 2026 07:19 PM</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1523,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="41.4" spans="1:40">
+    <row r="2" s="2" customFormat="1" ht="55.2" spans="1:40">
       <c r="A2" s="4" t="s">
         <v>40</v>
       </c>
@@ -1456,15 +1531,15 @@
         <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="D2" s="6" t="n">
         <f>C2+1</f>
-        <v>52340.0</v>
+        <v>8957.0</v>
       </c>
       <c r="E2" s="6" t="n">
         <f>D2</f>
-        <v>52340.0</v>
+        <v>8957.0</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1500,11 +1575,11 @@
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>52,340 km</v>
+        <v>8,957 km</v>
       </c>
       <c r="W2" s="7" t="s">
         <v>45</v>
@@ -1513,10 +1588,10 @@
         <v>46</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="AA2" s="7" t="s">
         <v>48</v>
@@ -1525,45 +1600,45 @@
         <v>49</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="AE2" s="7" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>Neil Jones</v>
+        <v>Sudeep Shakya</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="AH2" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AI2" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="AI2" s="7" t="s">
-        <v>84</v>
-      </c>
       <c r="AJ2" s="7" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
-        <v>MAZDA CX-5 - YKQ26Y</v>
+        <v>BYD DOLPHIN - FPJ50N</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="AM2" s="7" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AN2" s="7" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="82.8" spans="1:40">
+    <row r="3" s="2" customFormat="1" ht="55.2" spans="1:40">
       <c r="A3" s="4" t="s">
         <v>59</v>
       </c>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="141">
   <si>
     <t>TC ID</t>
   </si>
@@ -452,6 +452,13 @@
   </si>
   <si>
     <t>NQZAHJCYITFZBUAOEVZ SURRY HILLS NSW 2010</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+24,000 km</t>
+  </si>
+  <si>
+    <t>66 Talavera Rd MACQUARIE PARK NSW 2113</t>
   </si>
 </sst>
 </file>
@@ -1082,24 +1089,24 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3" t="str">
         <f>SUBSTITUTE(C2,"Latest Reading (kms)","")</f>
         <v xml:space="preserve">
-21,000 km</v>
+24,000 km</v>
       </c>
       <c r="E2" s="3" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(CLEAN(D2),"km",""),",","")," ",""),CHAR(160),"")</f>
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="F2" s="3" t="n">
         <f>E2+1</f>
-        <v>21001.0</v>
+        <v>24001.0</v>
       </c>
       <c r="G2" s="3" t="n">
         <f>F2</f>
-        <v>21001.0</v>
+        <v>24001.0</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>78</v>
@@ -1154,10 +1161,10 @@
       </c>
       <c r="Y2" s="4" t="str">
         <f>TEXT(G2,"#,##0")&amp;" km"</f>
-        <v>21,001 km</v>
+        <v>24,001 km</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="AA2" s="4" t="s">
         <v>133</v>
@@ -1185,7 +1192,7 @@
         <v>91</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AJ2" s="4" t="s">
         <v>93</v>
